--- a/output/VAT final report Q2'26.xlsx
+++ b/output/VAT final report Q2'26.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16956</v>
+        <v>19260</v>
       </c>
       <c r="D2" t="n">
-        <v>3561</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416047</v>
+        <v>416345</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>762976</v>
+        <v>771182</v>
       </c>
       <c r="D4" t="n">
-        <v>160225</v>
+        <v>161948</v>
       </c>
     </row>
     <row r="5">

--- a/output/VAT final report Q2'26.xlsx
+++ b/output/VAT final report Q2'26.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19260</v>
+        <v>22075</v>
       </c>
       <c r="D2" t="n">
-        <v>4045</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416345</v>
+        <v>1087727</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>771182</v>
+        <v>70681</v>
       </c>
       <c r="D4" t="n">
-        <v>161948</v>
+        <v>14843</v>
       </c>
     </row>
     <row r="5">

--- a/output/VAT final report Q2'26.xlsx
+++ b/output/VAT final report Q2'26.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22075</v>
+        <v>19260</v>
       </c>
       <c r="D2" t="n">
-        <v>4636</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1087727</v>
+        <v>416345</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70681</v>
+        <v>771182</v>
       </c>
       <c r="D4" t="n">
-        <v>14843</v>
+        <v>161948</v>
       </c>
     </row>
     <row r="5">
